--- a/DATA/GRASSES sheet.xlsx
+++ b/DATA/GRASSES sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\gumbo_dev\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471EE65A-DBA1-4952-8FE9-790C17061E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAADD3D8-32AA-479A-83C5-CD80D44D9081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="701" xr2:uid="{16A50922-D5D5-439E-954F-0577C856CD4C}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Grasses" sheetId="128" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Grasses!$I$1:$I$2454</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Grasses!$B$1:$B$2454</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -69593,6 +69593,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B1:B2454" xr:uid="{41E8FBF9-F009-4C0B-97E1-C217BDD2C623}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
